--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.50368134642024</v>
+        <v>5.119348218793289</v>
       </c>
       <c r="D2" t="n">
-        <v>30.52957264953611</v>
+        <v>4.961055555549618</v>
       </c>
       <c r="E2" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F2" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.61550442636481</v>
+        <v>4.812519469284282</v>
       </c>
       <c r="D3" t="n">
-        <v>29.19755213006264</v>
+        <v>4.74460222113518</v>
       </c>
       <c r="E3" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F3" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.15638609325778</v>
+        <v>3.762912740154389</v>
       </c>
       <c r="D4" t="n">
-        <v>23.05274919679466</v>
+        <v>3.746071744479132</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F4" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.52380691863716</v>
+        <v>6.260118624278538</v>
       </c>
       <c r="D5" t="n">
-        <v>66.04142275856209</v>
+        <v>10.73173119826634</v>
       </c>
       <c r="E5" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F5" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.76408947502953</v>
+        <v>3.699164539692299</v>
       </c>
       <c r="D6" t="n">
-        <v>55.37843617951627</v>
+        <v>8.998995879171394</v>
       </c>
       <c r="E6" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F6" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.96288525898425</v>
+        <v>1.131468854584941</v>
       </c>
       <c r="D7" t="n">
-        <v>42.95777055608612</v>
+        <v>6.980637715363995</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F7" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.31498890659835</v>
+        <v>8.013685697322233</v>
       </c>
       <c r="D8" t="n">
-        <v>61.58188360391664</v>
+        <v>10.00705608563645</v>
       </c>
       <c r="E8" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F8" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.46722317704208</v>
+        <v>5.763423766269338</v>
       </c>
       <c r="D9" t="n">
-        <v>38.138774777415</v>
+        <v>6.197550901329938</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F9" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.06707041446037</v>
+        <v>9.59839894234981</v>
       </c>
       <c r="D10" t="n">
-        <v>56.93387455682649</v>
+        <v>9.251754615484305</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F10" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.74678175722885</v>
+        <v>6.621352035549688</v>
       </c>
       <c r="D11" t="n">
-        <v>41.43075294842241</v>
+        <v>6.732497354118641</v>
       </c>
       <c r="E11" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F11" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.22989755784235</v>
+        <v>9.624858353149381</v>
       </c>
       <c r="D12" t="n">
-        <v>52.31156659860226</v>
+        <v>8.500629572272867</v>
       </c>
       <c r="E12" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F12" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>46.14682143567945</v>
+        <v>7.49885848329791</v>
       </c>
       <c r="D13" t="n">
-        <v>41.36725758374611</v>
+        <v>6.722179357358743</v>
       </c>
       <c r="E13" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F13" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.400461495739114</v>
+        <v>1.365074993057606</v>
       </c>
       <c r="D14" t="n">
-        <v>9.714066282017887</v>
+        <v>1.578535770827907</v>
       </c>
       <c r="E14" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F14" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.36746889894621</v>
+        <v>7.53471369607876</v>
       </c>
       <c r="D15" t="n">
-        <v>48.35194476050827</v>
+        <v>7.857191023582595</v>
       </c>
       <c r="E15" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F15" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.69936290621287</v>
+        <v>8.726146472259591</v>
       </c>
       <c r="D16" t="n">
-        <v>43.47700541665674</v>
+        <v>7.065013380206722</v>
       </c>
       <c r="E16" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F16" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7.267114640590615</v>
+        <v>1.180906129095975</v>
       </c>
       <c r="D17" t="n">
-        <v>7.171414855064598</v>
+        <v>1.165354913947997</v>
       </c>
       <c r="E17" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F17" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.0320331929361</v>
+        <v>5.692705393852116</v>
       </c>
       <c r="D18" t="n">
-        <v>23.44605782640749</v>
+        <v>3.809984396791217</v>
       </c>
       <c r="E18" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F18" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>45.20837343879067</v>
+        <v>7.346360683803484</v>
       </c>
       <c r="D19" t="n">
-        <v>47.33512440792779</v>
+        <v>7.691957716288266</v>
       </c>
       <c r="E19" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F19" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>68.21510774278113</v>
+        <v>11.08495500820193</v>
       </c>
       <c r="D20" t="n">
-        <v>48.00260409602796</v>
+        <v>7.800423165604544</v>
       </c>
       <c r="E20" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F20" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>35.47589891394372</v>
+        <v>5.764833573515856</v>
       </c>
       <c r="D21" t="n">
-        <v>7.778174593052023</v>
+        <v>1.263953371370954</v>
       </c>
       <c r="E21" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F21" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.38992186725819</v>
+        <v>6.075862303429456</v>
       </c>
       <c r="D22" t="n">
-        <v>37.96379854545643</v>
+        <v>6.169117263636671</v>
       </c>
       <c r="E22" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F22" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>56.3568907033446</v>
+        <v>9.157994739293498</v>
       </c>
       <c r="D23" t="n">
-        <v>58.35601756236797</v>
+        <v>9.482852853884795</v>
       </c>
       <c r="E23" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F23" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>41.27772620279621</v>
+        <v>6.707630507954384</v>
       </c>
       <c r="D24" t="n">
-        <v>32.19942667728549</v>
+        <v>5.232406835058893</v>
       </c>
       <c r="E24" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F24" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>63.27633055606419</v>
+        <v>10.28240371536043</v>
       </c>
       <c r="D25" t="n">
-        <v>59.57281051861175</v>
+        <v>9.68058170927441</v>
       </c>
       <c r="E25" t="n">
-        <v>16.71062062176418</v>
+        <v>2.715475851036679</v>
       </c>
       <c r="F25" t="n">
-        <v>16.60850510155479</v>
+        <v>2.698882079002654</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
